--- a/web/files/九龙-旺角-利奥坊．曦岸.xlsx
+++ b/web/files/九龙-旺角-利奥坊．曦岸.xlsx
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>8929300</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>22492</v>
+        <v>22379</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>8929300</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>22492</v>
+        <v>22379</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>15900000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>28649</v>
+        <v>29499</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>15900000</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>28649</v>
+        <v>29499</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>16500000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>25943</v>
+        <v>26190</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>16500000</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>25943</v>
+        <v>26190</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>382</v>
+        <v>268</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>8628800</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>22588</v>
+        <v>32197</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>8628800</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>22588</v>
+        <v>32197</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>255</v>
+        <v>375</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>6588000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>25835</v>
+        <v>17568</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>6588000</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>25835</v>
+        <v>17568</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>9806400</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>25739</v>
+        <v>25671</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>9806400</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>25739</v>
+        <v>25671</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>8274900</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>20134</v>
+        <v>20085</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>8274900</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>20134</v>
+        <v>20085</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>6904320</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>26865</v>
+        <v>26761</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>6904320</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>26865</v>
+        <v>26761</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>8106700</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>19724</v>
+        <v>19676</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>8106700</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>19724</v>
+        <v>19676</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>6450480</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>25099</v>
+        <v>25002</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>6450480</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>25099</v>
+        <v>25002</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>8052100</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>19591</v>
+        <v>19544</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>8052100</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>19591</v>
+        <v>19544</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>6407700</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>24933</v>
+        <v>24836</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>6407700</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>24933</v>
+        <v>24836</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>7998800</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>19462</v>
+        <v>19415</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>7998800</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>19462</v>
+        <v>19415</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>6364920</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>24766</v>
+        <v>24670</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>6364920</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>24766</v>
+        <v>24670</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>7944100</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>19329</v>
+        <v>19282</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>7944100</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>19329</v>
+        <v>19282</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>8001300</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>19468</v>
+        <v>19421</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>8001300</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>19468</v>
+        <v>19421</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>6345940</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>24692</v>
+        <v>24597</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>6345940</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>24692</v>
+        <v>24597</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>7817800</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>19068</v>
+        <v>19021</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>7817800</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>19068</v>
+        <v>19021</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>6259830</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>24263</v>
+        <v>24169</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>6259830</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>24263</v>
+        <v>24169</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>7763800</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>18936</v>
+        <v>18890</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>7763800</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>18936</v>
+        <v>18890</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>6216120</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>24093</v>
+        <v>24000</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>6216120</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>24093</v>
+        <v>24000</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>7818400</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>19069</v>
+        <v>19023</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>7818400</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>19069</v>
+        <v>19023</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>9164700</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>22353</v>
+        <v>22299</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>9164700</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>22353</v>
+        <v>22299</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>7601900</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>18541</v>
+        <v>18496</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>7601900</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>18541</v>
+        <v>18496</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>6481530</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>25122</v>
+        <v>25025</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>6481530</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>25122</v>
+        <v>25025</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>6110000</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>23682</v>
+        <v>23591</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>6110000</v>
       </c>
       <c r="L172" s="5" t="n">
-        <v>23682</v>
+        <v>23591</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>9986880</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>24358</v>
+        <v>24299</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>9986880</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>24358</v>
+        <v>24299</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         </is>
       </c>
       <c r="E228" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>5895270</v>
       </c>
       <c r="I228" s="5" t="n">
-        <v>22850</v>
+        <v>22762</v>
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>5895270</v>
       </c>
       <c r="L228" s="5" t="n">
-        <v>22850</v>
+        <v>22762</v>
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         </is>
       </c>
       <c r="E256" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>5787390</v>
       </c>
       <c r="I256" s="5" t="n">
-        <v>22432</v>
+        <v>22345</v>
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>5787390</v>
       </c>
       <c r="L256" s="5" t="n">
-        <v>22432</v>
+        <v>22345</v>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         </is>
       </c>
       <c r="E262" s="4" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>4200000</v>
       </c>
       <c r="I262" s="5" t="n">
-        <v>23464</v>
+        <v>23596</v>
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>4200000</v>
       </c>
       <c r="L262" s="5" t="n">
-        <v>23464</v>
+        <v>23596</v>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         </is>
       </c>
       <c r="E264" s="4" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>4150000</v>
       </c>
       <c r="I264" s="5" t="n">
-        <v>23851</v>
+        <v>23714</v>
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>4150000</v>
       </c>
       <c r="L264" s="5" t="n">
-        <v>23851</v>
+        <v>23714</v>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         </is>
       </c>
       <c r="E266" s="4" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>6400000</v>
       </c>
       <c r="I266" s="5" t="n">
-        <v>27706</v>
+        <v>27468</v>
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>6400000</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>27706</v>
+        <v>27468</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="E267" s="4" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>5800000</v>
       </c>
       <c r="I267" s="5" t="n">
-        <v>23868</v>
+        <v>23770</v>
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>5800000</v>
       </c>
       <c r="L267" s="5" t="n">
-        <v>23868</v>
+        <v>23770</v>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         </is>
       </c>
       <c r="E268" s="4" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>3800000</v>
       </c>
       <c r="I268" s="5" t="n">
-        <v>21348</v>
+        <v>21591</v>
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>3800000</v>
       </c>
       <c r="L268" s="5" t="n">
-        <v>21348</v>
+        <v>21591</v>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="E269" s="4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>9750000</v>
       </c>
       <c r="I269" s="5" t="n">
-        <v>26070</v>
+        <v>26139</v>
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>9750000</v>
       </c>
       <c r="L269" s="5" t="n">
-        <v>26070</v>
+        <v>26139</v>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         </is>
       </c>
       <c r="E270" s="4" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>5500000</v>
       </c>
       <c r="I270" s="5" t="n">
-        <v>23207</v>
+        <v>23109</v>
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>5500000</v>
       </c>
       <c r="L270" s="5" t="n">
-        <v>23207</v>
+        <v>23109</v>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         </is>
       </c>
       <c r="E278" s="4" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>18950000</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>28843</v>
+        <v>28887</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>18950000</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>28843</v>
+        <v>28887</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         </is>
       </c>
       <c r="E283" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>3889600</v>
       </c>
       <c r="I283" s="5" t="n">
-        <v>20049</v>
+        <v>20153</v>
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>3889600</v>
       </c>
       <c r="L283" s="5" t="n">
-        <v>20049</v>
+        <v>20153</v>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         </is>
       </c>
       <c r="E285" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>7763400</v>
       </c>
       <c r="I285" s="5" t="n">
-        <v>27145</v>
+        <v>27050</v>
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>7763400</v>
       </c>
       <c r="L285" s="5" t="n">
-        <v>27145</v>
+        <v>27050</v>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         </is>
       </c>
       <c r="E286" s="4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>10696050</v>
       </c>
       <c r="I286" s="5" t="n">
-        <v>26807</v>
+        <v>26740</v>
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>10696050</v>
       </c>
       <c r="L286" s="5" t="n">
-        <v>26807</v>
+        <v>26740</v>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         </is>
       </c>
       <c r="E290" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>6783980</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>27355</v>
+        <v>27466</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>6783980</v>
       </c>
       <c r="L290" s="5" t="n">
-        <v>27355</v>
+        <v>27466</v>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         </is>
       </c>
       <c r="E294" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>3806900</v>
       </c>
       <c r="I294" s="5" t="n">
-        <v>19623</v>
+        <v>19725</v>
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>3806900</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>19623</v>
+        <v>19725</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="E296" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>6331200</v>
       </c>
       <c r="I296" s="5" t="n">
-        <v>22137</v>
+        <v>22060</v>
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>6331200</v>
       </c>
       <c r="L296" s="5" t="n">
-        <v>22137</v>
+        <v>22060</v>
       </c>
       <c r="M296" s="3" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         </is>
       </c>
       <c r="E297" s="4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>10626700</v>
       </c>
       <c r="I297" s="5" t="n">
-        <v>26633</v>
+        <v>26567</v>
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>10626700</v>
       </c>
       <c r="L297" s="5" t="n">
-        <v>26633</v>
+        <v>26567</v>
       </c>
       <c r="M297" s="3" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         </is>
       </c>
       <c r="E301" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>6666240</v>
       </c>
       <c r="I301" s="5" t="n">
-        <v>26880</v>
+        <v>26989</v>
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>6666240</v>
       </c>
       <c r="L301" s="5" t="n">
-        <v>26880</v>
+        <v>26989</v>
       </c>
       <c r="M301" s="3" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         </is>
       </c>
       <c r="E303" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>6763050</v>
       </c>
       <c r="I303" s="5" t="n">
-        <v>26213</v>
+        <v>26112</v>
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>6763050</v>
       </c>
       <c r="L303" s="5" t="n">
-        <v>26213</v>
+        <v>26112</v>
       </c>
       <c r="M303" s="3" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         </is>
       </c>
       <c r="E305" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F305" s="3" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>5078700</v>
       </c>
       <c r="I305" s="5" t="n">
-        <v>26179</v>
+        <v>26315</v>
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>5078700</v>
       </c>
       <c r="L305" s="5" t="n">
-        <v>26179</v>
+        <v>26315</v>
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         </is>
       </c>
       <c r="E307" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>7499520</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>26222</v>
+        <v>26131</v>
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>7499520</v>
       </c>
       <c r="L307" s="5" t="n">
-        <v>26222</v>
+        <v>26131</v>
       </c>
       <c r="M307" s="3" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         </is>
       </c>
       <c r="E308" s="4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F308" s="3" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>10557350</v>
       </c>
       <c r="I308" s="5" t="n">
-        <v>26460</v>
+        <v>26393</v>
       </c>
       <c r="J308" s="3" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>10557350</v>
       </c>
       <c r="L308" s="5" t="n">
-        <v>26460</v>
+        <v>26393</v>
       </c>
       <c r="M308" s="3" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="E312" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>6693740</v>
       </c>
       <c r="I312" s="5" t="n">
-        <v>26991</v>
+        <v>27100</v>
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>6693740</v>
       </c>
       <c r="L312" s="5" t="n">
-        <v>26991</v>
+        <v>27100</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         </is>
       </c>
       <c r="E316" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F316" s="3" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>5325700</v>
       </c>
       <c r="I316" s="5" t="n">
-        <v>27452</v>
+        <v>27594</v>
       </c>
       <c r="J316" s="3" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>5325700</v>
       </c>
       <c r="L316" s="5" t="n">
-        <v>27452</v>
+        <v>27594</v>
       </c>
       <c r="M316" s="3" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         </is>
       </c>
       <c r="E318" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F318" s="3" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>6247000</v>
       </c>
       <c r="I318" s="5" t="n">
-        <v>21843</v>
+        <v>21767</v>
       </c>
       <c r="J318" s="3" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>6247000</v>
       </c>
       <c r="L318" s="5" t="n">
-        <v>21843</v>
+        <v>21767</v>
       </c>
       <c r="M318" s="3" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         </is>
       </c>
       <c r="E319" s="4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>9998430</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>25059</v>
+        <v>24996</v>
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>9998430</v>
       </c>
       <c r="L319" s="5" t="n">
-        <v>25059</v>
+        <v>24996</v>
       </c>
       <c r="M319" s="3" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         </is>
       </c>
       <c r="E327" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>5344320</v>
       </c>
       <c r="I327" s="5" t="n">
-        <v>27548</v>
+        <v>27691</v>
       </c>
       <c r="J327" s="3" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>5344320</v>
       </c>
       <c r="L327" s="5" t="n">
-        <v>27548</v>
+        <v>27691</v>
       </c>
       <c r="M327" s="3" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         </is>
       </c>
       <c r="E330" s="4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>9971520</v>
       </c>
       <c r="I330" s="5" t="n">
-        <v>24991</v>
+        <v>24929</v>
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>9971520</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>24991</v>
+        <v>24929</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         </is>
       </c>
       <c r="E336" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>6492580</v>
       </c>
       <c r="I336" s="5" t="n">
-        <v>25165</v>
+        <v>25068</v>
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>6492580</v>
       </c>
       <c r="L336" s="5" t="n">
-        <v>25165</v>
+        <v>25068</v>
       </c>
       <c r="M336" s="3" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         </is>
       </c>
       <c r="E340" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>7504050</v>
       </c>
       <c r="I340" s="5" t="n">
-        <v>26238</v>
+        <v>26147</v>
       </c>
       <c r="J340" s="3" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>7504050</v>
       </c>
       <c r="L340" s="5" t="n">
-        <v>26238</v>
+        <v>26147</v>
       </c>
       <c r="M340" s="3" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="E347" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>6381660</v>
       </c>
       <c r="I347" s="5" t="n">
-        <v>24735</v>
+        <v>24640</v>
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>6381660</v>
       </c>
       <c r="L347" s="5" t="n">
-        <v>24735</v>
+        <v>24640</v>
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         </is>
       </c>
       <c r="E356" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>6357480</v>
       </c>
       <c r="I356" s="5" t="n">
-        <v>25635</v>
+        <v>25739</v>
       </c>
       <c r="J356" s="3" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>6357480</v>
       </c>
       <c r="L356" s="5" t="n">
-        <v>25635</v>
+        <v>25739</v>
       </c>
       <c r="M356" s="3" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         </is>
       </c>
       <c r="E358" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>6407040</v>
       </c>
       <c r="I358" s="5" t="n">
-        <v>24833</v>
+        <v>24738</v>
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>6407040</v>
       </c>
       <c r="L358" s="5" t="n">
-        <v>24833</v>
+        <v>24738</v>
       </c>
       <c r="M358" s="3" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         </is>
       </c>
       <c r="E360" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>5126760</v>
       </c>
       <c r="I360" s="5" t="n">
-        <v>26427</v>
+        <v>26564</v>
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>5126760</v>
       </c>
       <c r="L360" s="5" t="n">
-        <v>26427</v>
+        <v>26564</v>
       </c>
       <c r="M360" s="3" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         </is>
       </c>
       <c r="E363" s="4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F363" s="3" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>9666420</v>
       </c>
       <c r="I363" s="5" t="n">
-        <v>24227</v>
+        <v>24166</v>
       </c>
       <c r="J363" s="3" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>9666420</v>
       </c>
       <c r="L363" s="5" t="n">
-        <v>24227</v>
+        <v>24166</v>
       </c>
       <c r="M363" s="3" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         </is>
       </c>
       <c r="E367" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>6313770</v>
       </c>
       <c r="I367" s="5" t="n">
-        <v>25459</v>
+        <v>25562</v>
       </c>
       <c r="J367" s="3" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>6313770</v>
       </c>
       <c r="L367" s="5" t="n">
-        <v>25459</v>
+        <v>25562</v>
       </c>
       <c r="M367" s="3" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         </is>
       </c>
       <c r="E369" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F369" s="3" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>6362860</v>
       </c>
       <c r="I369" s="5" t="n">
-        <v>24662</v>
+        <v>24567</v>
       </c>
       <c r="J369" s="3" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>6362860</v>
       </c>
       <c r="L369" s="5" t="n">
-        <v>24662</v>
+        <v>24567</v>
       </c>
       <c r="M369" s="3" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         </is>
       </c>
       <c r="E371" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F371" s="3" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>5091040</v>
       </c>
       <c r="I371" s="5" t="n">
-        <v>26242</v>
+        <v>26378</v>
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>5091040</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>26242</v>
+        <v>26378</v>
       </c>
       <c r="M371" s="3" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         </is>
       </c>
       <c r="E373" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F373" s="3" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>7088460</v>
       </c>
       <c r="I373" s="5" t="n">
-        <v>24785</v>
+        <v>24698</v>
       </c>
       <c r="J373" s="3" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>7088460</v>
       </c>
       <c r="L373" s="5" t="n">
-        <v>24785</v>
+        <v>24698</v>
       </c>
       <c r="M373" s="3" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         </is>
       </c>
       <c r="E378" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>6335600</v>
       </c>
       <c r="I378" s="5" t="n">
-        <v>25547</v>
+        <v>25650</v>
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>6335600</v>
       </c>
       <c r="L378" s="5" t="n">
-        <v>25547</v>
+        <v>25650</v>
       </c>
       <c r="M378" s="3" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         </is>
       </c>
       <c r="E380" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>6252390</v>
       </c>
       <c r="I380" s="5" t="n">
-        <v>24234</v>
+        <v>24141</v>
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>6252390</v>
       </c>
       <c r="L380" s="5" t="n">
-        <v>24234</v>
+        <v>24141</v>
       </c>
       <c r="M380" s="3" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         </is>
       </c>
       <c r="E382" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>5162880</v>
       </c>
       <c r="I382" s="5" t="n">
-        <v>26613</v>
+        <v>26751</v>
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>5162880</v>
       </c>
       <c r="L382" s="5" t="n">
-        <v>26613</v>
+        <v>26751</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         </is>
       </c>
       <c r="E389" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F389" s="3" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>6224490</v>
       </c>
       <c r="I389" s="5" t="n">
-        <v>25099</v>
+        <v>25200</v>
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>6224490</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>25099</v>
+        <v>25200</v>
       </c>
       <c r="M389" s="3" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         </is>
       </c>
       <c r="E393" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>5019600</v>
       </c>
       <c r="I393" s="5" t="n">
-        <v>25874</v>
+        <v>26008</v>
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>5019600</v>
       </c>
       <c r="L393" s="5" t="n">
-        <v>25874</v>
+        <v>26008</v>
       </c>
       <c r="M393" s="3" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         </is>
       </c>
       <c r="E400" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F400" s="3" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>6247240</v>
       </c>
       <c r="I400" s="5" t="n">
-        <v>25190</v>
+        <v>25292</v>
       </c>
       <c r="J400" s="3" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>6247240</v>
       </c>
       <c r="L400" s="5" t="n">
-        <v>25190</v>
+        <v>25292</v>
       </c>
       <c r="M400" s="3" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         </is>
       </c>
       <c r="E402" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>6233140</v>
       </c>
       <c r="I402" s="5" t="n">
-        <v>24159</v>
+        <v>24066</v>
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>6233140</v>
       </c>
       <c r="L402" s="5" t="n">
-        <v>24159</v>
+        <v>24066</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         </is>
       </c>
       <c r="E404" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F404" s="3" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>4966020</v>
       </c>
       <c r="I404" s="5" t="n">
-        <v>25598</v>
+        <v>25731</v>
       </c>
       <c r="J404" s="3" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>4966020</v>
       </c>
       <c r="L404" s="5" t="n">
-        <v>25598</v>
+        <v>25731</v>
       </c>
       <c r="M404" s="3" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         </is>
       </c>
       <c r="E407" s="4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F407" s="3" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>9534200</v>
       </c>
       <c r="I407" s="5" t="n">
-        <v>23895</v>
+        <v>23836</v>
       </c>
       <c r="J407" s="3" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>9534200</v>
       </c>
       <c r="L407" s="5" t="n">
-        <v>23895</v>
+        <v>23836</v>
       </c>
       <c r="M407" s="3" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         </is>
       </c>
       <c r="E411" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F411" s="3" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>6484500</v>
       </c>
       <c r="I411" s="5" t="n">
-        <v>26147</v>
+        <v>26253</v>
       </c>
       <c r="J411" s="3" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>6484500</v>
       </c>
       <c r="L411" s="5" t="n">
-        <v>26147</v>
+        <v>26253</v>
       </c>
       <c r="M411" s="3" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         </is>
       </c>
       <c r="E413" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F413" s="3" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>6188960</v>
       </c>
       <c r="I413" s="5" t="n">
-        <v>23988</v>
+        <v>23896</v>
       </c>
       <c r="J413" s="3" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>6188960</v>
       </c>
       <c r="L413" s="5" t="n">
-        <v>23988</v>
+        <v>23896</v>
       </c>
       <c r="M413" s="3" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         </is>
       </c>
       <c r="E415" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>4912440</v>
       </c>
       <c r="I415" s="5" t="n">
-        <v>25322</v>
+        <v>25453</v>
       </c>
       <c r="J415" s="3" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>4912440</v>
       </c>
       <c r="L415" s="5" t="n">
-        <v>25322</v>
+        <v>25453</v>
       </c>
       <c r="M415" s="3" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         </is>
       </c>
       <c r="E422" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>6455000</v>
       </c>
       <c r="I422" s="5" t="n">
-        <v>26028</v>
+        <v>26134</v>
       </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>6455000</v>
       </c>
       <c r="L422" s="5" t="n">
-        <v>26028</v>
+        <v>26134</v>
       </c>
       <c r="M422" s="3" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         </is>
       </c>
       <c r="E424" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F424" s="3" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>6145720</v>
       </c>
       <c r="I424" s="5" t="n">
-        <v>23821</v>
+        <v>23729</v>
       </c>
       <c r="J424" s="3" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>6145720</v>
       </c>
       <c r="L424" s="5" t="n">
-        <v>23821</v>
+        <v>23729</v>
       </c>
       <c r="M424" s="3" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         </is>
       </c>
       <c r="E426" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>4841000</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>24954</v>
+        <v>25083</v>
       </c>
       <c r="J426" s="3" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>4841000</v>
       </c>
       <c r="L426" s="5" t="n">
-        <v>24954</v>
+        <v>25083</v>
       </c>
       <c r="M426" s="3" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         </is>
       </c>
       <c r="E428" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F428" s="3" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>7125000</v>
       </c>
       <c r="I428" s="5" t="n">
-        <v>24913</v>
+        <v>24826</v>
       </c>
       <c r="J428" s="3" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>7125000</v>
       </c>
       <c r="L428" s="5" t="n">
-        <v>24913</v>
+        <v>24826</v>
       </c>
       <c r="M428" s="3" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         </is>
       </c>
       <c r="E433" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>5959440</v>
       </c>
       <c r="I433" s="5" t="n">
-        <v>24030</v>
+        <v>24127</v>
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>5959440</v>
       </c>
       <c r="L433" s="5" t="n">
-        <v>24030</v>
+        <v>24127</v>
       </c>
       <c r="M433" s="3" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         </is>
       </c>
       <c r="E435" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F435" s="3" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>6037560</v>
       </c>
       <c r="I435" s="5" t="n">
-        <v>23401</v>
+        <v>23311</v>
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>6037560</v>
       </c>
       <c r="L435" s="5" t="n">
-        <v>23401</v>
+        <v>23311</v>
       </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         </is>
       </c>
       <c r="E437" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F437" s="3" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>4754160</v>
       </c>
       <c r="I437" s="5" t="n">
-        <v>24506</v>
+        <v>24633</v>
       </c>
       <c r="J437" s="3" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>4754160</v>
       </c>
       <c r="L437" s="5" t="n">
-        <v>24506</v>
+        <v>24633</v>
       </c>
       <c r="M437" s="3" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         </is>
       </c>
       <c r="E439" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F439" s="3" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>6760480</v>
       </c>
       <c r="I439" s="5" t="n">
-        <v>23638</v>
+        <v>23556</v>
       </c>
       <c r="J439" s="3" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>6760480</v>
       </c>
       <c r="L439" s="5" t="n">
-        <v>23638</v>
+        <v>23556</v>
       </c>
       <c r="M439" s="3" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         </is>
       </c>
       <c r="E444" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F444" s="3" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>5978400</v>
       </c>
       <c r="I444" s="5" t="n">
-        <v>24106</v>
+        <v>24204</v>
       </c>
       <c r="J444" s="3" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>5978400</v>
       </c>
       <c r="L444" s="5" t="n">
-        <v>24106</v>
+        <v>24204</v>
       </c>
       <c r="M444" s="3" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         </is>
       </c>
       <c r="E446" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F446" s="3" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>5994780</v>
       </c>
       <c r="I446" s="5" t="n">
-        <v>23236</v>
+        <v>23146</v>
       </c>
       <c r="J446" s="3" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>5994780</v>
       </c>
       <c r="L446" s="5" t="n">
-        <v>23236</v>
+        <v>23146</v>
       </c>
       <c r="M446" s="3" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         </is>
       </c>
       <c r="E448" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F448" s="3" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>4787420</v>
       </c>
       <c r="I448" s="5" t="n">
-        <v>24677</v>
+        <v>24805</v>
       </c>
       <c r="J448" s="3" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>4787420</v>
       </c>
       <c r="L448" s="5" t="n">
-        <v>24677</v>
+        <v>24805</v>
       </c>
       <c r="M448" s="3" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         </is>
       </c>
       <c r="E451" s="4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F451" s="3" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>9130220</v>
       </c>
       <c r="I451" s="5" t="n">
-        <v>22883</v>
+        <v>22826</v>
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>9130220</v>
       </c>
       <c r="L451" s="5" t="n">
-        <v>22883</v>
+        <v>22826</v>
       </c>
       <c r="M451" s="3" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="E455" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F455" s="3" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>5955840</v>
       </c>
       <c r="I455" s="5" t="n">
-        <v>24015</v>
+        <v>24113</v>
       </c>
       <c r="J455" s="3" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>5955840</v>
       </c>
       <c r="L455" s="5" t="n">
-        <v>24015</v>
+        <v>24113</v>
       </c>
       <c r="M455" s="3" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         </is>
       </c>
       <c r="E457" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F457" s="3" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>5973390</v>
       </c>
       <c r="I457" s="5" t="n">
-        <v>23153</v>
+        <v>23063</v>
       </c>
       <c r="J457" s="3" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>5973390</v>
       </c>
       <c r="L457" s="5" t="n">
-        <v>23153</v>
+        <v>23063</v>
       </c>
       <c r="M457" s="3" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         </is>
       </c>
       <c r="E459" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F459" s="3" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>4701150</v>
       </c>
       <c r="I459" s="5" t="n">
-        <v>24233</v>
+        <v>24358</v>
       </c>
       <c r="J459" s="3" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>4701150</v>
       </c>
       <c r="L459" s="5" t="n">
-        <v>24233</v>
+        <v>24358</v>
       </c>
       <c r="M459" s="3" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         </is>
       </c>
       <c r="E461" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F461" s="3" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>6684340</v>
       </c>
       <c r="I461" s="5" t="n">
-        <v>23372</v>
+        <v>23290</v>
       </c>
       <c r="J461" s="3" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>6684340</v>
       </c>
       <c r="L461" s="5" t="n">
-        <v>23372</v>
+        <v>23290</v>
       </c>
       <c r="M461" s="3" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         </is>
       </c>
       <c r="E468" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F468" s="3" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>6236580</v>
       </c>
       <c r="I468" s="5" t="n">
-        <v>24173</v>
+        <v>24079</v>
       </c>
       <c r="J468" s="3" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>6236580</v>
       </c>
       <c r="L468" s="5" t="n">
-        <v>24173</v>
+        <v>24079</v>
       </c>
       <c r="M468" s="3" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         </is>
       </c>
       <c r="E470" s="4" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F470" s="3" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>4648140</v>
       </c>
       <c r="I470" s="5" t="n">
-        <v>23959</v>
+        <v>24084</v>
       </c>
       <c r="J470" s="3" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>4648140</v>
       </c>
       <c r="L470" s="5" t="n">
-        <v>23959</v>
+        <v>24084</v>
       </c>
       <c r="M470" s="3" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         </is>
       </c>
       <c r="E473" s="4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F473" s="3" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>8962900</v>
       </c>
       <c r="I473" s="5" t="n">
-        <v>22463</v>
+        <v>22407</v>
       </c>
       <c r="J473" s="3" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>8962900</v>
       </c>
       <c r="L473" s="5" t="n">
-        <v>22463</v>
+        <v>22407</v>
       </c>
       <c r="M473" s="3" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         </is>
       </c>
       <c r="E477" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F477" s="3" t="inlineStr">
         <is>
@@ -30168,7 +30168,7 @@
         <v>5844920</v>
       </c>
       <c r="I477" s="5" t="n">
-        <v>23568</v>
+        <v>23664</v>
       </c>
       <c r="J477" s="3" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>5844920</v>
       </c>
       <c r="L477" s="5" t="n">
-        <v>23568</v>
+        <v>23664</v>
       </c>
       <c r="M477" s="3" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="E479" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F479" s="3" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>6168690</v>
       </c>
       <c r="I479" s="5" t="n">
-        <v>23910</v>
+        <v>23817</v>
       </c>
       <c r="J479" s="3" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>6168690</v>
       </c>
       <c r="L479" s="5" t="n">
-        <v>23910</v>
+        <v>23817</v>
       </c>
       <c r="M479" s="3" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         </is>
       </c>
       <c r="E480" s="4" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F480" s="3" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>4900000</v>
       </c>
       <c r="I480" s="5" t="n">
-        <v>28161</v>
+        <v>28000</v>
       </c>
       <c r="J480" s="3" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>4900000</v>
       </c>
       <c r="L480" s="5" t="n">
-        <v>28161</v>
+        <v>28000</v>
       </c>
       <c r="M480" s="3" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         </is>
       </c>
       <c r="E485" s="4" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F485" s="3" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>6180000</v>
       </c>
       <c r="I485" s="5" t="n">
-        <v>26186</v>
+        <v>26298</v>
       </c>
       <c r="J485" s="3" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>6180000</v>
       </c>
       <c r="L485" s="5" t="n">
-        <v>26186</v>
+        <v>26298</v>
       </c>
       <c r="M485" s="3" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         </is>
       </c>
       <c r="E486" s="4" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F486" s="3" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>5200000</v>
       </c>
       <c r="I486" s="5" t="n">
-        <v>22034</v>
+        <v>22128</v>
       </c>
       <c r="J486" s="3" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>5200000</v>
       </c>
       <c r="L486" s="5" t="n">
-        <v>22034</v>
+        <v>22128</v>
       </c>
       <c r="M486" s="3" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         </is>
       </c>
       <c r="E487" s="4" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F487" s="3" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>6300000</v>
       </c>
       <c r="I487" s="5" t="n">
-        <v>26695</v>
+        <v>26809</v>
       </c>
       <c r="J487" s="3" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>6300000</v>
       </c>
       <c r="L487" s="5" t="n">
-        <v>26695</v>
+        <v>26809</v>
       </c>
       <c r="M487" s="3" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         </is>
       </c>
       <c r="E488" s="4" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F488" s="3" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>6100000</v>
       </c>
       <c r="I488" s="5" t="n">
-        <v>26991</v>
+        <v>27111</v>
       </c>
       <c r="J488" s="3" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>6100000</v>
       </c>
       <c r="L488" s="5" t="n">
-        <v>26991</v>
+        <v>27111</v>
       </c>
       <c r="M488" s="3" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         </is>
       </c>
       <c r="E489" s="4" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F489" s="3" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>8750000</v>
       </c>
       <c r="I489" s="5" t="n">
-        <v>23271</v>
+        <v>23333</v>
       </c>
       <c r="J489" s="3" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>8750000</v>
       </c>
       <c r="L489" s="5" t="n">
-        <v>23271</v>
+        <v>23333</v>
       </c>
       <c r="M489" s="3" t="inlineStr">
         <is>
@@ -31189,49 +31189,49 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 381呎 (2房)
+          <t>A | 382呎 (2房)
 $981万
-$25,739/呎
+$25,671/呎
 (23年-02月-09日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>B | 255呎 (2房)
+          <t>B | 375呎 (2房)
 $659万
-$25,835/呎
+$17,568/呎
 (23年-02月-28日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>C | 382呎 (1房)
+          <t>C | 268呎 (1房)
 $863万
-$22,588/呎
+$32,197/呎
 (23年-12月-29日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>D | 636呎 (3房)
+          <t>D | 630呎 (3房)
 $1650万
-$25,943/呎
+$26,190/呎
 (24年-04月-11日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>E | 555呎 (2房)
+          <t>E | 539呎 (2房)
 $1590万
-$28,649/呎
+$29,499/呎
 (22年-08月-23日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
-          <t>F | 397呎 (2房)
+          <t>F | 399呎 (2房)
 $893万
-$22,492/呎
+$22,379/呎
 (23年-12月-13日)</t>
         </is>
       </c>
@@ -31299,17 +31299,17 @@
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>F | 257呎 (1房)
+          <t>F | 258呎 (1房)
 $690万
-$26,865/呎
+$26,761/呎
 (21年-07月-30日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>G | 411呎 (2房)
+          <t>G | 412呎 (2房)
 $827万
-$20,134/呎
+$20,085/呎
 (24年-03月-22日)</t>
         </is>
       </c>
@@ -31418,17 +31418,17 @@
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>F | 257呎 (1房)
+          <t>F | 258呎 (1房)
 $645万
-$25,099/呎
+$25,002/呎
 (20年-12月-31日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>G | 411呎 (2房)
+          <t>G | 412呎 (2房)
 $811万
-$19,724/呎
+$19,676/呎
 (24年-03月-25日)</t>
         </is>
       </c>
@@ -31537,17 +31537,17 @@
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>F | 257呎 (1房)
+          <t>F | 258呎 (1房)
 $641万
-$24,933/呎
+$24,836/呎
 (21年-05月-17日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>G | 411呎 (2房)
+          <t>G | 412呎 (2房)
 $805万
-$19,591/呎
+$19,544/呎
 (24年-03月-14日)</t>
         </is>
       </c>
@@ -31656,17 +31656,17 @@
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>F | 257呎 (1房)
+          <t>F | 258呎 (1房)
 $636万
-$24,766/呎
+$24,670/呎
 (21年-05月-17日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>G | 411呎 (2房)
+          <t>G | 412呎 (2房)
 $800万
-$19,462/呎
+$19,415/呎
 (24年-03月-27日)</t>
         </is>
       </c>
@@ -31783,9 +31783,9 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>G | 411呎 (2房)
+          <t>G | 412呎 (2房)
 $794万
-$19,329/呎
+$19,282/呎
 (24年-04月-05日)</t>
         </is>
       </c>
@@ -31894,17 +31894,17 @@
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>F | 257呎 (1房)
+          <t>F | 258呎 (1房)
 $635万
-$24,692/呎
+$24,597/呎
 (20年-11月-17日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>G | 411呎 (2房)
+          <t>G | 412呎 (2房)
 $800万
-$19,468/呎
+$19,421/呎
 (24年-03月-22日)</t>
         </is>
       </c>
@@ -32013,17 +32013,17 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>F | 258呎 (1房)
+          <t>F | 259呎 (1房)
 $626万
-$24,263/呎
+$24,169/呎
 (21年-02月-01日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>G | 410呎 (2房)
+          <t>G | 411呎 (2房)
 $782万
-$19,068/呎
+$19,021/呎
 (24年-03月-21日)</t>
         </is>
       </c>
@@ -32132,17 +32132,17 @@
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>F | 258呎 (1房)
+          <t>F | 259呎 (1房)
 $622万
-$24,093/呎
+$24,000/呎
 (21年-04月-22日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>G | 410呎 (2房)
+          <t>G | 411呎 (2房)
 $776万
-$18,936/呎
+$18,890/呎
 (24年-03月-21日)</t>
         </is>
       </c>
@@ -32259,9 +32259,9 @@
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>G | 410呎 (2房)
+          <t>G | 411呎 (2房)
 $782万
-$19,069/呎
+$19,023/呎
 (24年-03月-22日)</t>
         </is>
       </c>
@@ -32378,9 +32378,9 @@
       </c>
       <c r="H15" s="20" t="inlineStr">
         <is>
-          <t>G | 410呎 (2房)
+          <t>G | 411呎 (2房)
 $916万
-$22,353/呎
+$22,299/呎
 (23年-09月-29日)</t>
         </is>
       </c>
@@ -32489,17 +32489,17 @@
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>F | 258呎 (1房)
+          <t>F | 259呎 (1房)
 $648万
-$25,122/呎
+$25,025/呎
 (20年-12月-22日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>G | 410呎 (2房)
+          <t>G | 411呎 (2房)
 $760万
-$18,541/呎
+$18,496/呎
 (24年-03月-18日)</t>
         </is>
       </c>
@@ -32608,9 +32608,9 @@
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>F | 258呎 (1房)
+          <t>F | 259呎 (1房)
 $611万
-$23,682/呎
+$23,591/呎
 (20年-11月-30日)</t>
         </is>
       </c>
@@ -32973,9 +32973,9 @@
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>G | 410呎 (2房)
+          <t>G | 411呎 (2房)
 $999万
-$24,358/呎
+$24,299/呎
 (21年-07月-07日)</t>
         </is>
       </c>
@@ -33084,9 +33084,9 @@
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>F | 258呎 (1房)
+          <t>F | 259呎 (1房)
 $590万
-$22,850/呎
+$22,762/呎
 (20年-12月-08日)</t>
         </is>
       </c>
@@ -33322,9 +33322,9 @@
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>F | 258呎 (1房)
+          <t>F | 259呎 (1房)
 $579万
-$22,432/呎
+$22,345/呎
 (20年-11月-10日)</t>
         </is>
       </c>
@@ -33441,41 +33441,41 @@
       </c>
       <c r="G24" s="20" t="inlineStr">
         <is>
-          <t>F | 237呎 (1房)
+          <t>F | 238呎 (1房)
 $550万
-$23,207/呎
+$23,109/呎
 (25年-12月-24日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
         <is>
-          <t>G | 374呎 (2房)
+          <t>G | 373呎 (2房)
 $975万
-$26,070/呎
+$26,139/呎
 (23年-02月-06日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
-          <t>H | 178呎 (开放式)
+          <t>H | 176呎 (开放式)
 $380万
-$21,348/呎
+$21,591/呎
 (25年-10月-09日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>J | 243呎 (1房)
+          <t>J | 244呎 (1房)
 $580万
-$23,868/呎
+$23,770/呎
 (25年-11月-17日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
         <is>
-          <t>K | 231呎 (1房)
+          <t>K | 233呎 (1房)
 $640万
-$27,706/呎
+$27,468/呎
 (22年-09月-28日)</t>
         </is>
       </c>
@@ -33489,9 +33489,9 @@
       </c>
       <c r="M24" s="20" t="inlineStr">
         <is>
-          <t>M | 174呎 (开放式)
+          <t>M | 175呎 (开放式)
 $415万
-$23,851/呎
+$23,714/呎
 (25年-12月-11日)</t>
         </is>
       </c>
@@ -33505,9 +33505,9 @@
       </c>
       <c r="O24" s="20" t="inlineStr">
         <is>
-          <t>P | 179呎 (开放式)
+          <t>P | 178呎 (开放式)
 $420万
-$23,464/呎
+$23,596/呎
 (25年-10月-17日)</t>
         </is>
       </c>
@@ -33709,9 +33709,9 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>D | 657呎 (3房)
+          <t>D | 656呎 (3房)
 $1895万
-$28,843/呎
+$28,887/呎
 (25年-08月-12日)</t>
         </is>
       </c>
@@ -33761,9 +33761,9 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $678万
-$27,355/呎
+$27,466/呎
 (21年-06月-08日)</t>
         </is>
       </c>
@@ -33793,17 +33793,17 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>G | 399呎 (2房)
+          <t>G | 400呎 (2房)
 $1070万
-$26,807/呎
+$26,740/呎
 (21年-07月-29日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>H | 286呎 (1房)
+          <t>H | 287呎 (1房)
 $776万
-$27,145/呎
+$27,050/呎
 (21年-12月-23日)</t>
         </is>
       </c>
@@ -33817,9 +33817,9 @@
       </c>
       <c r="K6" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $389万
-$20,049/呎
+$20,153/呎
 (25年-09月-17日)</t>
         </is>
       </c>
@@ -33840,9 +33840,9 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $676万
-$26,213/呎
+$26,112/呎
 (21年-07月-05日)</t>
         </is>
       </c>
@@ -33856,9 +33856,9 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $667万
-$26,880/呎
+$26,989/呎
 (21年-06月-07日)</t>
         </is>
       </c>
@@ -33888,17 +33888,17 @@
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>G | 399呎 (2房)
+          <t>G | 400呎 (2房)
 $1063万
-$26,633/呎
+$26,567/呎
 (21年-08月-31日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>H | 286呎 (1房)
+          <t>H | 287呎 (1房)
 $633万
-$22,137/呎
+$22,060/呎
 (24年-03月-21日)</t>
         </is>
       </c>
@@ -33912,9 +33912,9 @@
       </c>
       <c r="K7" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $381万
-$19,623/呎
+$19,725/呎
 (25年-08月-25日)</t>
         </is>
       </c>
@@ -33951,9 +33951,9 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $669万
-$26,991/呎
+$27,100/呎
 (21年-05月-11日)</t>
         </is>
       </c>
@@ -33983,17 +33983,17 @@
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>G | 399呎 (2房)
+          <t>G | 400呎 (2房)
 $1056万
-$26,460/呎
+$26,393/呎
 (21年-08月-31日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
         <is>
-          <t>H | 286呎 (1房)
+          <t>H | 287呎 (1房)
 $750万
-$26,222/呎
+$26,131/呎
 (22年-08月-16日)</t>
         </is>
       </c>
@@ -34007,9 +34007,9 @@
       </c>
       <c r="K8" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $508万
-$26,179/呎
+$26,315/呎
 (23年-03月-10日)</t>
         </is>
       </c>
@@ -34078,17 +34078,17 @@
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>G | 399呎 (2房)
+          <t>G | 400呎 (2房)
 $1000万
-$25,059/呎
+$24,996/呎
 (21年-06月-09日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>H | 286呎 (1房)
+          <t>H | 287呎 (1房)
 $625万
-$21,843/呎
+$21,767/呎
 (24年-03月-27日)</t>
         </is>
       </c>
@@ -34102,9 +34102,9 @@
       </c>
       <c r="K9" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $533万
-$27,452/呎
+$27,594/呎
 (21年-10月-07日)</t>
         </is>
       </c>
@@ -34125,9 +34125,9 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $649万
-$25,165/呎
+$25,068/呎
 (21年-06月-17日)</t>
         </is>
       </c>
@@ -34173,9 +34173,9 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>G | 399呎 (2房)
+          <t>G | 400呎 (2房)
 $997万
-$24,991/呎
+$24,929/呎
 (21年-05月-25日)</t>
         </is>
       </c>
@@ -34197,9 +34197,9 @@
       </c>
       <c r="K10" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $534万
-$27,548/呎
+$27,691/呎
 (21年-09月-09日)</t>
         </is>
       </c>
@@ -34220,9 +34220,9 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $638万
-$24,735/呎
+$24,640/呎
 (21年-05月-02日)</t>
         </is>
       </c>
@@ -34276,9 +34276,9 @@
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>H | 286呎 (1房)
+          <t>H | 287呎 (1房)
 $750万
-$26,238/呎
+$26,147/呎
 (22年-04月-27日)</t>
         </is>
       </c>
@@ -34315,9 +34315,9 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $641万
-$24,833/呎
+$24,738/呎
 (21年-05月-24日)</t>
         </is>
       </c>
@@ -34331,9 +34331,9 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $636万
-$25,635/呎
+$25,739/呎
 (21年-02月-08日)</t>
         </is>
       </c>
@@ -34410,9 +34410,9 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $636万
-$24,662/呎
+$24,567/呎
 (21年-05月-07日)</t>
         </is>
       </c>
@@ -34426,9 +34426,9 @@
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $631万
-$25,459/呎
+$25,562/呎
 (21年-02月-01日)</t>
         </is>
       </c>
@@ -34458,9 +34458,9 @@
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>G | 399呎 (2房)
+          <t>G | 400呎 (2房)
 $967万
-$24,227/呎
+$24,166/呎
 (21年-05月-28日)</t>
         </is>
       </c>
@@ -34482,9 +34482,9 @@
       </c>
       <c r="K13" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $513万
-$26,427/呎
+$26,564/呎
 (21年-05月-28日)</t>
         </is>
       </c>
@@ -34505,9 +34505,9 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $625万
-$24,234/呎
+$24,141/呎
 (21年-05月-05日)</t>
         </is>
       </c>
@@ -34521,9 +34521,9 @@
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $634万
-$25,547/呎
+$25,650/呎
 (21年-02月-08日)</t>
         </is>
       </c>
@@ -34561,9 +34561,9 @@
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>H | 286呎 (1房)
+          <t>H | 287呎 (1房)
 $709万
-$24,785/呎
+$24,698/呎
 (21年-05月-31日)</t>
         </is>
       </c>
@@ -34577,9 +34577,9 @@
       </c>
       <c r="K14" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $509万
-$26,242/呎
+$26,378/呎
 (20年-11月-11日)</t>
         </is>
       </c>
@@ -34616,9 +34616,9 @@
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $622万
-$25,099/呎
+$25,200/呎
 (20年-12月-30日)</t>
         </is>
       </c>
@@ -34672,9 +34672,9 @@
       </c>
       <c r="K15" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $516万
-$26,613/呎
+$26,751/呎
 (21年-06月-30日)</t>
         </is>
       </c>
@@ -34695,9 +34695,9 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $623万
-$24,159/呎
+$24,066/呎
 (21年-05月-24日)</t>
         </is>
       </c>
@@ -34711,9 +34711,9 @@
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $625万
-$25,190/呎
+$25,292/呎
 (20年-10月-30日)</t>
         </is>
       </c>
@@ -34767,9 +34767,9 @@
       </c>
       <c r="K16" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $502万
-$25,874/呎
+$26,008/呎
 (21年-03月-24日)</t>
         </is>
       </c>
@@ -34790,9 +34790,9 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $619万
-$23,988/呎
+$23,896/呎
 (21年-05月-13日)</t>
         </is>
       </c>
@@ -34806,9 +34806,9 @@
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $648万
-$26,147/呎
+$26,253/呎
 (21年-02月-10日)</t>
         </is>
       </c>
@@ -34838,9 +34838,9 @@
       </c>
       <c r="H17" s="20" t="inlineStr">
         <is>
-          <t>G | 399呎 (2房)
+          <t>G | 400呎 (2房)
 $953万
-$23,895/呎
+$23,836/呎
 (21年-06月-23日)</t>
         </is>
       </c>
@@ -34862,9 +34862,9 @@
       </c>
       <c r="K17" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $497万
-$25,598/呎
+$25,731/呎
 (20年-08月-03日)</t>
         </is>
       </c>
@@ -34885,9 +34885,9 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $615万
-$23,821/呎
+$23,729/呎
 (21年-04月-14日)</t>
         </is>
       </c>
@@ -34901,9 +34901,9 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $646万
-$26,028/呎
+$26,134/呎
 (20年-10月-08日)</t>
         </is>
       </c>
@@ -34957,9 +34957,9 @@
       </c>
       <c r="K18" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $491万
-$25,322/呎
+$25,453/呎
 (20年-08月-03日)</t>
         </is>
       </c>
@@ -34980,9 +34980,9 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $604万
-$23,401/呎
+$23,311/呎
 (21年-02月-26日)</t>
         </is>
       </c>
@@ -34996,9 +34996,9 @@
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $596万
-$24,030/呎
+$24,127/呎
 (20年-08月-20日)</t>
         </is>
       </c>
@@ -35036,9 +35036,9 @@
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
-          <t>H | 286呎 (1房)
+          <t>H | 287呎 (1房)
 $712万
-$24,913/呎
+$24,826/呎
 (21年-09月-16日)</t>
         </is>
       </c>
@@ -35052,9 +35052,9 @@
       </c>
       <c r="K19" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $484万
-$24,954/呎
+$25,083/呎
 (20年-06月-18日)</t>
         </is>
       </c>
@@ -35075,9 +35075,9 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $599万
-$23,236/呎
+$23,146/呎
 (21年-02月-23日)</t>
         </is>
       </c>
@@ -35091,9 +35091,9 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $598万
-$24,106/呎
+$24,204/呎
 (20年-09月-09日)</t>
         </is>
       </c>
@@ -35131,9 +35131,9 @@
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
-          <t>H | 286呎 (1房)
+          <t>H | 287呎 (1房)
 $676万
-$23,638/呎
+$23,556/呎
 (21年-06月-08日)</t>
         </is>
       </c>
@@ -35147,9 +35147,9 @@
       </c>
       <c r="K20" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $475万
-$24,506/呎
+$24,633/呎
 (20年-06月-19日)</t>
         </is>
       </c>
@@ -35170,9 +35170,9 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $597万
-$23,153/呎
+$23,063/呎
 (21年-01月-23日)</t>
         </is>
       </c>
@@ -35186,9 +35186,9 @@
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $596万
-$24,015/呎
+$24,113/呎
 (20年-08月-18日)</t>
         </is>
       </c>
@@ -35218,9 +35218,9 @@
       </c>
       <c r="H21" s="20" t="inlineStr">
         <is>
-          <t>G | 399呎 (2房)
+          <t>G | 400呎 (2房)
 $913万
-$22,883/呎
+$22,826/呎
 (21年-06月-08日)</t>
         </is>
       </c>
@@ -35242,9 +35242,9 @@
       </c>
       <c r="K21" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $479万
-$24,677/呎
+$24,805/呎
 (20年-06月-18日)</t>
         </is>
       </c>
@@ -35265,9 +35265,9 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $624万
-$24,173/呎
+$24,079/呎
 (21年-06月-11日)</t>
         </is>
       </c>
@@ -35321,9 +35321,9 @@
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
-          <t>H | 286呎 (1房)
+          <t>H | 287呎 (1房)
 $668万
-$23,372/呎
+$23,290/呎
 (21年-06月-01日)</t>
         </is>
       </c>
@@ -35337,9 +35337,9 @@
       </c>
       <c r="K22" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $470万
-$24,233/呎
+$24,358/呎
 (20年-06月-22日)</t>
         </is>
       </c>
@@ -35360,9 +35360,9 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 258呎 (1房)
+          <t>A | 259呎 (1房)
 $617万
-$23,910/呎
+$23,817/呎
 (21年-05月-27日)</t>
         </is>
       </c>
@@ -35376,9 +35376,9 @@
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $584万
-$23,568/呎
+$23,664/呎
 (20年-08月-18日)</t>
         </is>
       </c>
@@ -35408,9 +35408,9 @@
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>G | 399呎 (2房)
+          <t>G | 400呎 (2房)
 $896万
-$22,463/呎
+$22,407/呎
 (21年-05月-11日)</t>
         </is>
       </c>
@@ -35432,9 +35432,9 @@
       </c>
       <c r="K23" s="20" t="inlineStr">
         <is>
-          <t>K | 194呎 (开放式)
+          <t>K | 193呎 (开放式)
 $465万
-$23,959/呎
+$24,084/呎
 (20年-06月-23日)</t>
         </is>
       </c>
@@ -35463,41 +35463,41 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 376呎 (2房)
+          <t>B | 375呎 (2房)
 $875万
-$23,271/呎
+$23,333/呎
 (25年-12月-18日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>C | 226呎 (1房)
+          <t>C | 225呎 (1房)
 $610万
-$26,991/呎
+$27,111/呎
 (22年-09月-14日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>D | 236呎 (1房)
+          <t>D | 235呎 (1房)
 $630万
-$26,695/呎
+$26,809/呎
 (22年-08月-24日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>E | 236呎 (1房)
+          <t>E | 235呎 (1房)
 $520万
-$22,034/呎
+$22,128/呎
 (25年-11月-06日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
         <is>
-          <t>F | 236呎 (1房)
+          <t>F | 235呎 (1房)
 $618万
-$26,186/呎
+$26,298/呎
 (22年-08月-24日)</t>
         </is>
       </c>
@@ -35535,9 +35535,9 @@
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
-          <t>L | 174呎 (开放式)
+          <t>L | 175呎 (开放式)
 $490万
-$28,161/呎
+$28,000/呎
 (22年-10月-11日)</t>
         </is>
       </c>
